--- a/Evaluation/dm_test/dm_test_results_by_coin.xlsx
+++ b/Evaluation/dm_test/dm_test_results_by_coin.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.613</v>
+        <v>-1.198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.27</v>
+        <v>0.885</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.055</v>
+        <v>-1.511</v>
       </c>
       <c r="E6" t="n">
-        <v>0.522</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>0.549</v>
       </c>
       <c r="E10" t="n">
-        <v>0.54</v>
+        <v>0.291</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.386</v>
+        <v>-2.39</v>
       </c>
       <c r="E14" t="n">
-        <v>0.65</v>
+        <v>0.992</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.655</v>
+        <v>-0.222</v>
       </c>
       <c r="E18" t="n">
-        <v>0.256</v>
+        <v>0.588</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.17</v>
+        <v>-2.049</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-1.493</v>
+        <v>-1.962</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.855</v>
+        <v>-1.088</v>
       </c>
       <c r="E30" t="n">
-        <v>0.804</v>
+        <v>0.862</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.241</v>
+        <v>0.31</v>
       </c>
       <c r="E34" t="n">
-        <v>0.405</v>
+        <v>0.378</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.164</v>
+        <v>0.106</v>
       </c>
       <c r="E38" t="n">
-        <v>0.435</v>
+        <v>0.458</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.348</v>
+        <v>-0.308</v>
       </c>
       <c r="E42" t="n">
-        <v>0.636</v>
+        <v>0.621</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.145</v>
+        <v>-0.91</v>
       </c>
       <c r="E46" t="n">
-        <v>0.126</v>
+        <v>0.819</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
